--- a/data/trans_dic/P70B_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P70B_R-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que concilia su vida profesional y laboral</t>
+          <t>Población que concilia su vida profesional y laboral (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,88; 86,31</t>
+          <t>52,07; 86,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>77,44; 95,08</t>
+          <t>76,81; 94,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67,17; 87,7</t>
+          <t>67,09; 87,44</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>81,42; 90,93</t>
+          <t>80,85; 90,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,22; 93,83</t>
+          <t>81,86; 93,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,46; 91,06</t>
+          <t>83,65; 91,0</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>78,59; 86,5</t>
+          <t>78,88; 86,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,92; 86,24</t>
+          <t>79,72; 86,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,29; 85,26</t>
+          <t>80,17; 85,28</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>85,13; 96,07</t>
+          <t>85,46; 96,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81,99; 89,51</t>
+          <t>81,88; 89,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,07; 94,14</t>
+          <t>85,43; 94,35</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>82,68; 89,9</t>
+          <t>82,72; 89,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>83,21; 90,46</t>
+          <t>83,23; 90,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84,17; 89,63</t>
+          <t>84,01; 89,2</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93,86; 100,0</t>
+          <t>93,9; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82,01; 100,0</t>
+          <t>85,02; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91,42; 100,0</t>
+          <t>91,82; 100,0</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>84,17; 90,95</t>
+          <t>84,0; 91,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>83,89; 88,28</t>
+          <t>83,94; 88,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84,78; 89,35</t>
+          <t>84,67; 89,29</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que concilia su vida profesional y laboral</t>
+          <t>Población que concilia su vida profesional y laboral (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>47298; 75773</t>
+          <t>45711; 76005</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62914; 77244</t>
+          <t>62401; 77151</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>113534; 148238</t>
+          <t>113394; 147799</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>285233; 318574</t>
+          <t>283265; 318371</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>290159; 331134</t>
+          <t>288894; 330742</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>586910; 640359</t>
+          <t>588307; 639957</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>361656; 398030</t>
+          <t>363000; 397219</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>279814; 301945</t>
+          <t>279097; 302115</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>650540; 690839</t>
+          <t>649578; 690991</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>635320; 716920</t>
+          <t>637747; 719924</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>371236; 405293</t>
+          <t>370732; 405569</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1020006; 1128803</t>
+          <t>1024297; 1131238</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>248278; 269984</t>
+          <t>248406; 270232</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>172399; 187417</t>
+          <t>172422; 187506</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>427127; 454877</t>
+          <t>426344; 452686</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15902; 16943</t>
+          <t>15909; 16943</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14558; 17751</t>
+          <t>15092; 17751</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31718; 34694</t>
+          <t>31857; 34694</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>688; 1598</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>688; 1598</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1652582; 1785734</t>
+          <t>1649331; 1795233</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1226398; 1290624</t>
+          <t>1227209; 1292206</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2904039; 3060596</t>
+          <t>2900291; 3058549</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P70B_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P70B_R-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>80,95%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,07; 86,58</t>
+          <t>60,28; 87,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76,81; 94,97</t>
+          <t>76,96; 94,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67,09; 87,44</t>
+          <t>70,34; 88,38</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>80,85; 90,87</t>
+          <t>80,57; 90,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>81,86; 93,72</t>
+          <t>81,55; 89,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,65; 91,0</t>
+          <t>82,62; 88,92</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,84%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>78,88; 86,32</t>
+          <t>80,86; 87,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,72; 86,29</t>
+          <t>79,58; 86,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,17; 85,28</t>
+          <t>81,09; 85,95</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>86,14%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>85,46; 96,47</t>
+          <t>83,11; 89,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81,88; 89,57</t>
+          <t>83,35; 88,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,43; 94,35</t>
+          <t>83,92; 88,15</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,37%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>82,72; 89,99</t>
+          <t>83,73; 90,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>83,23; 90,51</t>
+          <t>83,67; 90,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84,01; 89,2</t>
+          <t>84,79; 89,82</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93,9; 100,0</t>
+          <t>82,53; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85,02; 100,0</t>
+          <t>84,91; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91,82; 100,0</t>
+          <t>89,67; 100,0</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>85,52%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>84,0; 91,43</t>
+          <t>83,5; 87,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>83,94; 88,39</t>
+          <t>84,01; 87,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84,67; 89,29</t>
+          <t>84,24; 86,71</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>63386</t>
+          <t>76376</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>71455</t>
+          <t>80516</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>134842</t>
+          <t>156891</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>45711; 76005</t>
+          <t>61530; 89307</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62401; 77151</t>
+          <t>70603; 86581</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>113394; 147799</t>
+          <t>136333; 171291</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>303275</t>
+          <t>341463</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>308709</t>
+          <t>273280</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>611983</t>
+          <t>614743</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>283265; 318371</t>
+          <t>318976; 357900</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>288894; 330742</t>
+          <t>260321; 287104</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>588307; 639957</t>
+          <t>590819; 635883</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>381206</t>
+          <t>450778</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>291003</t>
+          <t>329052</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>672209</t>
+          <t>779828</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>363000; 397219</t>
+          <t>432204; 468995</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>279097; 302115</t>
+          <t>314827; 341231</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>649578; 690991</t>
+          <t>754246; 799412</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>677757</t>
+          <t>470863</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>388578</t>
+          <t>390099</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1066335</t>
+          <t>860962</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>637747; 719924</t>
+          <t>452639; 486657</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>370732; 405569</t>
+          <t>379079; 402584</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1024297; 1131238</t>
+          <t>838774; 881059</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>260286</t>
+          <t>287615</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>180738</t>
+          <t>203040</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>441024</t>
+          <t>490656</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>248406; 270232</t>
+          <t>275797; 298470</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>172422; 187506</t>
+          <t>194261; 210615</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>426344; 452686</t>
+          <t>476152; 504400</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>16776</t>
+          <t>18447</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>17185</t>
+          <t>19151</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33962</t>
+          <t>37599</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15909; 16943</t>
+          <t>15818; 19166</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15092; 17751</t>
+          <t>16745; 19720</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31857; 34694</t>
+          <t>34869; 38886</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1704284</t>
+          <t>1647358</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1257670</t>
+          <t>1295137</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2961954</t>
+          <t>2942495</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1649331; 1795233</t>
+          <t>1609585; 1682397</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1227209; 1292206</t>
+          <t>1271312; 1320028</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2900291; 3058549</t>
+          <t>2898616; 2983553</t>
         </is>
       </c>
     </row>
